--- a/cost-plans/Urban-Highway-Improvement-Scheme.xlsx
+++ b/cost-plans/Urban-Highway-Improvement-Scheme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\qs\project-cost-control\cost-plans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40886D22-99F8-430B-9CBE-F902E144B72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D075570-FCE9-4D2B-9F85-FA1AAA67A567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14092" activeTab="1" xr2:uid="{0C8C6BE1-598D-4333-9AA5-A074653745B1}"/>
   </bookViews>
@@ -522,12 +522,6 @@
     <xf numFmtId="9" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="1" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -539,8 +533,8 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="38" fontId="0" fillId="5" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -553,6 +547,12 @@
     <xf numFmtId="165" fontId="0" fillId="5" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Accent1" xfId="1" builtinId="29"/>
@@ -681,6 +681,14 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.17769945846356505"/>
+          <c:y val="0"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -756,14 +764,43 @@
           </c:marker>
           <c:dLbls>
             <c:dLbl>
-              <c:idx val="5"/>
+              <c:idx val="18"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-1.6969695761016267E-2"/>
-                  <c:y val="7.1065502058144367E-2"/>
+                  <c:x val="-1.5467172101605925E-2"/>
+                  <c:y val="7.9329881130107249E-2"/>
                 </c:manualLayout>
               </c:layout>
-              <c:dLblPos val="r"/>
+              <c:numFmt formatCode="&quot;£&quot;#,##0.0,,&quot;M&quot;" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="75000"/>
+                          <a:lumOff val="25000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
@@ -773,11 +810,10 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-8567-424D-8F78-650AFDB2B1C9}"/>
+                  <c16:uniqueId val="{00000000-C5A1-4BB2-81B8-6F9D14B124BD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
-            <c:numFmt formatCode="&quot;£&quot;#,##0.0,,&quot;M&quot;" sourceLinked="0"/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -1012,14 +1048,13 @@
           </c:marker>
           <c:dLbls>
             <c:dLbl>
-              <c:idx val="5"/>
+              <c:idx val="18"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-8.2400114740059094E-2"/>
-                  <c:y val="-6.0082038925462183E-2"/>
+                  <c:x val="-7.0707072464484225E-2"/>
+                  <c:y val="-4.8287753731369634E-2"/>
                 </c:manualLayout>
               </c:layout>
-              <c:dLblPos val="r"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
               <c:showCatName val="0"/>
@@ -1029,7 +1064,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-8567-424D-8F78-650AFDB2B1C9}"/>
+                  <c16:uniqueId val="{00000001-C5A1-4BB2-81B8-6F9D14B124BD}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1978,15 +2013,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>223157</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>106135</xdr:rowOff>
+      <xdr:colOff>114299</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>8164</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>451756</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>636813</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>174171</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2367,33 +2402,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="35.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
     </row>
     <row r="2" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="34" t="str">
+      <c r="A2" s="59" t="str">
         <f ca="1">"Meridian Cost Consultants | Report Date: "&amp;TEXT(TODAY(),"DD MMMM YYYY")</f>
-        <v>Meridian Cost Consultants | Report Date: 14 May 2026</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
+        <v>Meridian Cost Consultants | Report Date: 15 May 2026</v>
+      </c>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
@@ -2434,31 +2469,31 @@
       <c r="B5" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="33">
         <f>SUM(C6:C8)</f>
         <v>1280000</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="33">
         <f t="shared" ref="D5:H5" si="0">SUM(D6:D8)</f>
         <v>180000</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="33">
         <f t="shared" si="0"/>
         <v>1460000</v>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="33">
         <f t="shared" si="0"/>
         <v>1440000</v>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="33">
         <f t="shared" si="0"/>
         <v>1340000</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="33">
         <f t="shared" si="0"/>
         <v>1580000</v>
       </c>
-      <c r="I5" s="36">
+      <c r="I5" s="34">
         <f>E5-H5</f>
         <v>-120000</v>
       </c>
@@ -2474,24 +2509,24 @@
       <c r="B6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="35">
         <v>640000</v>
       </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37">
+      <c r="D6" s="35"/>
+      <c r="E6" s="35">
         <f t="shared" ref="E6:E25" si="1">SUM(C6:D6)</f>
         <v>640000</v>
       </c>
-      <c r="F6" s="37">
+      <c r="F6" s="35">
         <v>640000</v>
       </c>
-      <c r="G6" s="37">
+      <c r="G6" s="35">
         <v>640000</v>
       </c>
-      <c r="H6" s="37">
+      <c r="H6" s="35">
         <v>640000</v>
       </c>
-      <c r="I6" s="38">
+      <c r="I6" s="36">
         <f t="shared" ref="I6:I25" si="2">E6-H6</f>
         <v>0</v>
       </c>
@@ -2506,24 +2541,24 @@
       <c r="B7" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="37">
         <v>320000</v>
       </c>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39">
+      <c r="D7" s="37"/>
+      <c r="E7" s="37">
         <f t="shared" si="1"/>
         <v>320000</v>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="37">
         <v>320000</v>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="37">
         <v>320000</v>
       </c>
-      <c r="H7" s="39">
+      <c r="H7" s="37">
         <v>320000</v>
       </c>
-      <c r="I7" s="40">
+      <c r="I7" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2538,26 +2573,26 @@
       <c r="B8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="35">
         <v>320000</v>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="35">
         <v>180000</v>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="35">
         <f t="shared" ref="E8" si="3">SUM(C8:D8)</f>
         <v>500000</v>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="35">
         <v>480000</v>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="35">
         <v>380000</v>
       </c>
-      <c r="H8" s="37">
+      <c r="H8" s="35">
         <v>620000</v>
       </c>
-      <c r="I8" s="38">
+      <c r="I8" s="36">
         <f t="shared" ref="I8" si="4">E8-H8</f>
         <v>-120000</v>
       </c>
@@ -2572,31 +2607,31 @@
       <c r="B9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="33">
         <f>SUM(C10:C12)</f>
         <v>6400000</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="33">
         <f t="shared" ref="D9:G9" si="5">SUM(D10:D12)</f>
         <v>95000</v>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="33">
         <f t="shared" si="5"/>
         <v>6495000</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="33">
         <f t="shared" si="5"/>
         <v>5695000</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="33">
         <f t="shared" si="5"/>
         <v>4560000</v>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="33">
         <f>SUM(H10:H12)</f>
         <v>7100000</v>
       </c>
-      <c r="I9" s="36">
+      <c r="I9" s="34">
         <f t="shared" si="2"/>
         <v>-605000</v>
       </c>
@@ -2612,26 +2647,26 @@
       <c r="B10" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="35">
         <v>3200000</v>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="35">
         <v>95000</v>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="35">
         <f t="shared" si="1"/>
         <v>3295000</v>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="35">
         <v>3295000</v>
       </c>
-      <c r="G10" s="37">
+      <c r="G10" s="35">
         <v>2640000</v>
       </c>
-      <c r="H10" s="37">
+      <c r="H10" s="35">
         <v>3580000</v>
       </c>
-      <c r="I10" s="38">
+      <c r="I10" s="36">
         <f t="shared" si="2"/>
         <v>-285000</v>
       </c>
@@ -2646,24 +2681,24 @@
       <c r="B11" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="37">
         <v>2240000</v>
       </c>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39">
+      <c r="D11" s="37"/>
+      <c r="E11" s="37">
         <f t="shared" si="1"/>
         <v>2240000</v>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="37">
         <v>1680000</v>
       </c>
-      <c r="G11" s="39">
+      <c r="G11" s="37">
         <v>1344000</v>
       </c>
-      <c r="H11" s="39">
+      <c r="H11" s="37">
         <v>2420000</v>
       </c>
-      <c r="I11" s="40">
+      <c r="I11" s="38">
         <f t="shared" si="2"/>
         <v>-180000</v>
       </c>
@@ -2678,24 +2713,24 @@
       <c r="B12" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="37">
+      <c r="C12" s="35">
         <v>960000</v>
       </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37">
+      <c r="D12" s="35"/>
+      <c r="E12" s="35">
         <f t="shared" si="1"/>
         <v>960000</v>
       </c>
-      <c r="F12" s="37">
+      <c r="F12" s="35">
         <v>720000</v>
       </c>
-      <c r="G12" s="37">
+      <c r="G12" s="35">
         <v>576000</v>
       </c>
-      <c r="H12" s="37">
+      <c r="H12" s="35">
         <v>1100000</v>
       </c>
-      <c r="I12" s="38">
+      <c r="I12" s="36">
         <f t="shared" si="2"/>
         <v>-140000</v>
       </c>
@@ -2710,31 +2745,31 @@
       <c r="B13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="33">
         <f>SUM(C14:C15)</f>
         <v>5760000</v>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="33">
         <f t="shared" ref="D13:H13" si="6">SUM(D14:D15)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="33">
         <f t="shared" si="6"/>
         <v>5760000</v>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="33">
         <f t="shared" si="6"/>
         <v>3328000</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="33">
         <f t="shared" si="6"/>
         <v>1664000</v>
       </c>
-      <c r="H13" s="35">
+      <c r="H13" s="33">
         <f t="shared" si="6"/>
         <v>5760000</v>
       </c>
-      <c r="I13" s="36">
+      <c r="I13" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2750,24 +2785,24 @@
       <c r="B14" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="35">
         <v>4480000</v>
       </c>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37">
+      <c r="D14" s="35"/>
+      <c r="E14" s="35">
         <f t="shared" si="1"/>
         <v>4480000</v>
       </c>
-      <c r="F14" s="37">
+      <c r="F14" s="35">
         <v>2688000</v>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="35">
         <v>1344000</v>
       </c>
-      <c r="H14" s="37">
+      <c r="H14" s="35">
         <v>4480000</v>
       </c>
-      <c r="I14" s="38">
+      <c r="I14" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2782,24 +2817,24 @@
       <c r="B15" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="37">
         <v>1280000</v>
       </c>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39">
+      <c r="D15" s="37"/>
+      <c r="E15" s="37">
         <f t="shared" si="1"/>
         <v>1280000</v>
       </c>
-      <c r="F15" s="39">
+      <c r="F15" s="37">
         <v>640000</v>
       </c>
-      <c r="G15" s="39">
+      <c r="G15" s="37">
         <v>320000</v>
       </c>
-      <c r="H15" s="39">
+      <c r="H15" s="37">
         <v>1280000</v>
       </c>
-      <c r="I15" s="40">
+      <c r="I15" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2814,31 +2849,31 @@
       <c r="B16" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="33">
         <f>SUM(C17:C19)</f>
         <v>7040000</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="33">
         <f t="shared" ref="D16:H16" si="7">SUM(D17:D19)</f>
         <v>220000</v>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="33">
         <f t="shared" si="7"/>
         <v>7260000</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="33">
         <f t="shared" si="7"/>
         <v>5664000</v>
       </c>
-      <c r="G16" s="35">
+      <c r="G16" s="33">
         <f t="shared" si="7"/>
         <v>3648000</v>
       </c>
-      <c r="H16" s="35">
+      <c r="H16" s="33">
         <f t="shared" si="7"/>
         <v>7650000</v>
       </c>
-      <c r="I16" s="36">
+      <c r="I16" s="34">
         <f t="shared" si="2"/>
         <v>-390000</v>
       </c>
@@ -2854,26 +2889,26 @@
       <c r="B17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="35">
         <v>4800000</v>
       </c>
-      <c r="D17" s="37">
+      <c r="D17" s="35">
         <v>220000</v>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="35">
         <f t="shared" si="1"/>
         <v>5020000</v>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="35">
         <v>4320000</v>
       </c>
-      <c r="G17" s="37">
+      <c r="G17" s="35">
         <v>2880000</v>
       </c>
-      <c r="H17" s="37">
+      <c r="H17" s="35">
         <v>5200000</v>
       </c>
-      <c r="I17" s="38">
+      <c r="I17" s="36">
         <f t="shared" si="2"/>
         <v>-180000</v>
       </c>
@@ -2888,24 +2923,24 @@
       <c r="B18" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="39">
+      <c r="C18" s="37">
         <v>1600000</v>
       </c>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39">
+      <c r="D18" s="37"/>
+      <c r="E18" s="37">
         <f t="shared" si="1"/>
         <v>1600000</v>
       </c>
-      <c r="F18" s="39">
+      <c r="F18" s="37">
         <v>960000</v>
       </c>
-      <c r="G18" s="39">
+      <c r="G18" s="37">
         <v>576000</v>
       </c>
-      <c r="H18" s="39">
+      <c r="H18" s="37">
         <v>1750000</v>
       </c>
-      <c r="I18" s="40">
+      <c r="I18" s="38">
         <f t="shared" si="2"/>
         <v>-150000</v>
       </c>
@@ -2920,24 +2955,24 @@
       <c r="B19" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="37">
+      <c r="C19" s="35">
         <v>640000</v>
       </c>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37">
+      <c r="D19" s="35"/>
+      <c r="E19" s="35">
         <f t="shared" si="1"/>
         <v>640000</v>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="35">
         <v>384000</v>
       </c>
-      <c r="G19" s="37">
+      <c r="G19" s="35">
         <v>192000</v>
       </c>
-      <c r="H19" s="37">
+      <c r="H19" s="35">
         <v>700000</v>
       </c>
-      <c r="I19" s="38">
+      <c r="I19" s="36">
         <f t="shared" si="2"/>
         <v>-60000</v>
       </c>
@@ -2952,31 +2987,31 @@
       <c r="B20" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="33">
         <f>SUM(C21:C22)</f>
         <v>2560000</v>
       </c>
-      <c r="D20" s="35">
+      <c r="D20" s="33">
         <f t="shared" ref="D20:H20" si="8">SUM(D21:D22)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="33">
         <f t="shared" si="8"/>
         <v>2560000</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="33">
         <f t="shared" si="8"/>
         <v>928000</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="33">
         <f t="shared" si="8"/>
         <v>464000</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="33">
         <f t="shared" si="8"/>
         <v>2560000</v>
       </c>
-      <c r="I20" s="36">
+      <c r="I20" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2992,24 +3027,24 @@
       <c r="B21" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="37">
+      <c r="C21" s="35">
         <v>1600000</v>
       </c>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37">
+      <c r="D21" s="35"/>
+      <c r="E21" s="35">
         <f t="shared" si="1"/>
         <v>1600000</v>
       </c>
-      <c r="F21" s="37">
+      <c r="F21" s="35">
         <v>640000</v>
       </c>
-      <c r="G21" s="37">
+      <c r="G21" s="35">
         <v>320000</v>
       </c>
-      <c r="H21" s="37">
+      <c r="H21" s="35">
         <v>1600000</v>
       </c>
-      <c r="I21" s="38">
+      <c r="I21" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3024,24 +3059,24 @@
       <c r="B22" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="39">
+      <c r="C22" s="37">
         <v>960000</v>
       </c>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39">
+      <c r="D22" s="37"/>
+      <c r="E22" s="37">
         <f t="shared" si="1"/>
         <v>960000</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="37">
         <v>288000</v>
       </c>
-      <c r="G22" s="39">
+      <c r="G22" s="37">
         <v>144000</v>
       </c>
-      <c r="H22" s="39">
+      <c r="H22" s="37">
         <v>960000</v>
       </c>
-      <c r="I22" s="40">
+      <c r="I22" s="38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3056,24 +3091,24 @@
       <c r="B23" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="33">
         <v>960000</v>
       </c>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35">
+      <c r="D23" s="33"/>
+      <c r="E23" s="33">
         <f t="shared" si="1"/>
         <v>960000</v>
       </c>
-      <c r="F23" s="35">
+      <c r="F23" s="33">
         <v>192000</v>
       </c>
-      <c r="G23" s="35">
+      <c r="G23" s="33">
         <v>0</v>
       </c>
-      <c r="H23" s="35">
+      <c r="H23" s="33">
         <v>960000</v>
       </c>
-      <c r="I23" s="36">
+      <c r="I23" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3088,26 +3123,26 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="33">
         <v>5760000</v>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="33">
         <v>145000</v>
       </c>
-      <c r="E24" s="35">
+      <c r="E24" s="33">
         <f t="shared" si="1"/>
         <v>5905000</v>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="33">
         <v>5905000</v>
       </c>
-      <c r="G24" s="35">
+      <c r="G24" s="33">
         <v>2962500</v>
       </c>
-      <c r="H24" s="35">
+      <c r="H24" s="33">
         <v>6200000</v>
       </c>
-      <c r="I24" s="36">
+      <c r="I24" s="34">
         <f t="shared" si="2"/>
         <v>-295000</v>
       </c>
@@ -3122,24 +3157,24 @@
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="33">
         <v>2240000</v>
       </c>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35">
+      <c r="D25" s="33"/>
+      <c r="E25" s="33">
         <f t="shared" si="1"/>
         <v>2240000</v>
       </c>
-      <c r="F25" s="35">
+      <c r="F25" s="33">
         <v>0</v>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="33">
         <v>0</v>
       </c>
-      <c r="H25" s="35">
+      <c r="H25" s="33">
         <v>1800000</v>
       </c>
-      <c r="I25" s="36">
+      <c r="I25" s="34">
         <f t="shared" si="2"/>
         <v>440000</v>
       </c>
@@ -3151,31 +3186,31 @@
       <c r="B26" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="41">
+      <c r="C26" s="39">
         <f>SUM(C5,C9,C13,C16,C20,C23,C24,C25)</f>
         <v>32000000</v>
       </c>
-      <c r="D26" s="41">
+      <c r="D26" s="39">
         <f t="shared" ref="D26:H26" si="9">SUM(D5,D9,D13,D16,D20,D23,D24,D25)</f>
         <v>640000</v>
       </c>
-      <c r="E26" s="41">
+      <c r="E26" s="39">
         <f t="shared" si="9"/>
         <v>32640000</v>
       </c>
-      <c r="F26" s="41">
+      <c r="F26" s="39">
         <f t="shared" si="9"/>
         <v>23152000</v>
       </c>
-      <c r="G26" s="41">
+      <c r="G26" s="39">
         <f t="shared" si="9"/>
         <v>14638500</v>
       </c>
-      <c r="H26" s="41">
+      <c r="H26" s="39">
         <f t="shared" si="9"/>
         <v>33610000</v>
       </c>
-      <c r="I26" s="42">
+      <c r="I26" s="40">
         <f>E26-H26</f>
         <v>-970000</v>
       </c>
@@ -3221,73 +3256,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="35.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="44" t="s">
+      <c r="F4" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="45" t="s">
+      <c r="G4" s="43" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A5" s="52">
+      <c r="A5" s="50">
         <v>45170</v>
       </c>
-      <c r="B5" s="53">
+      <c r="B5" s="51">
         <v>480000</v>
       </c>
-      <c r="C5" s="53">
+      <c r="C5" s="51">
         <v>510000</v>
       </c>
-      <c r="D5" s="54">
+      <c r="D5" s="52">
         <f>B5-C5</f>
         <v>-30000</v>
       </c>
-      <c r="E5" s="55">
+      <c r="E5" s="53">
         <f>D5/B5</f>
         <v>-6.25E-2</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="54">
         <f>B5/C5</f>
         <v>0.94117647058823528</v>
       </c>
-      <c r="G5" s="57">
+      <c r="G5" s="55">
         <f>'Cost Plan'!$E$26/F5</f>
         <v>34680000</v>
       </c>
@@ -3310,7 +3345,7 @@
         <f t="shared" ref="E6:E10" si="1">D6/B6</f>
         <v>-7.1428571428571425E-2</v>
       </c>
-      <c r="F6" s="47">
+      <c r="F6" s="45">
         <f t="shared" ref="F6:F10" si="2">B6/C6</f>
         <v>0.93333333333333335</v>
       </c>
@@ -3337,7 +3372,7 @@
         <f t="shared" si="1"/>
         <v>-7.8787878787878782E-2</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="44">
         <f t="shared" si="2"/>
         <v>0.9269662921348315</v>
       </c>
@@ -3364,7 +3399,7 @@
         <f t="shared" si="1"/>
         <v>-8.5714285714285715E-2</v>
       </c>
-      <c r="F8" s="47">
+      <c r="F8" s="45">
         <f t="shared" si="2"/>
         <v>0.92105263157894735</v>
       </c>
@@ -3391,7 +3426,7 @@
         <f t="shared" si="1"/>
         <v>-8.1560283687943269E-2</v>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="44">
         <f t="shared" si="2"/>
         <v>0.92459016393442628</v>
       </c>
@@ -3418,7 +3453,7 @@
         <f t="shared" si="1"/>
         <v>-8.1521739130434784E-2</v>
       </c>
-      <c r="F10" s="47">
+      <c r="F10" s="45">
         <f t="shared" si="2"/>
         <v>0.92462311557788945</v>
       </c>
@@ -3445,7 +3480,7 @@
         <f t="shared" ref="E11:E23" si="4">D11/B11</f>
         <v>-6.6666666666666666E-2</v>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="44">
         <f t="shared" ref="F11:F23" si="5">B11/C11</f>
         <v>0.9375</v>
       </c>
@@ -3472,7 +3507,7 @@
         <f t="shared" si="4"/>
         <v>-6.0897435897435896E-2</v>
       </c>
-      <c r="F12" s="47">
+      <c r="F12" s="45">
         <f t="shared" si="5"/>
         <v>0.94259818731117828</v>
       </c>
@@ -3499,7 +3534,7 @@
         <f t="shared" si="4"/>
         <v>-5.46875E-2</v>
       </c>
-      <c r="F13" s="46">
+      <c r="F13" s="44">
         <f t="shared" si="5"/>
         <v>0.94814814814814818</v>
       </c>
@@ -3526,7 +3561,7 @@
         <f t="shared" si="4"/>
         <v>-5.8114035087719298E-2</v>
       </c>
-      <c r="F14" s="47">
+      <c r="F14" s="45">
         <f t="shared" si="5"/>
         <v>0.94507772020725389</v>
       </c>
@@ -3553,7 +3588,7 @@
         <f t="shared" si="4"/>
         <v>-5.587121212121212E-2</v>
       </c>
-      <c r="F15" s="46">
+      <c r="F15" s="44">
         <f t="shared" si="5"/>
         <v>0.94708520179372202</v>
       </c>
@@ -3580,7 +3615,7 @@
         <f t="shared" si="4"/>
         <v>-5.5084745762711863E-2</v>
       </c>
-      <c r="F16" s="47">
+      <c r="F16" s="45">
         <f t="shared" si="5"/>
         <v>0.94779116465863456</v>
       </c>
@@ -3607,7 +3642,7 @@
         <f t="shared" si="4"/>
         <v>-5.4054054054054057E-2</v>
       </c>
-      <c r="F17" s="46">
+      <c r="F17" s="44">
         <f t="shared" si="5"/>
         <v>0.94871794871794868</v>
       </c>
@@ -3634,7 +3669,7 @@
         <f t="shared" si="4"/>
         <v>-5.2442528735632182E-2</v>
       </c>
-      <c r="F18" s="47">
+      <c r="F18" s="45">
         <f t="shared" si="5"/>
         <v>0.95017064846416377</v>
       </c>
@@ -3661,7 +3696,7 @@
         <f t="shared" si="4"/>
         <v>-5.2559726962457337E-2</v>
       </c>
-      <c r="F19" s="46">
+      <c r="F19" s="44">
         <f t="shared" si="5"/>
         <v>0.95006485084306092</v>
       </c>
@@ -3688,7 +3723,7 @@
         <f t="shared" si="4"/>
         <v>-5.2356020942408377E-2</v>
       </c>
-      <c r="F20" s="47">
+      <c r="F20" s="45">
         <f t="shared" si="5"/>
         <v>0.95024875621890548</v>
       </c>
@@ -3715,7 +3750,7 @@
         <f t="shared" si="4"/>
         <v>-5.2465233881163087E-2</v>
       </c>
-      <c r="F21" s="46">
+      <c r="F21" s="44">
         <f t="shared" si="5"/>
         <v>0.95015015015015014</v>
       </c>
@@ -3742,7 +3777,7 @@
         <f t="shared" si="4"/>
         <v>-5.2307692307692305E-2</v>
       </c>
-      <c r="F22" s="47">
+      <c r="F22" s="45">
         <f t="shared" si="5"/>
         <v>0.95029239766081874</v>
       </c>
@@ -3752,28 +3787,28 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A23" s="58">
+      <c r="A23" s="56">
         <v>45717</v>
       </c>
-      <c r="B23" s="48">
+      <c r="B23" s="46">
         <v>16640000</v>
       </c>
-      <c r="C23" s="48">
+      <c r="C23" s="46">
         <v>17610000</v>
       </c>
-      <c r="D23" s="49">
+      <c r="D23" s="47">
         <f t="shared" si="3"/>
         <v>-970000</v>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="48">
         <f t="shared" si="4"/>
         <v>-5.8293269230769232E-2</v>
       </c>
-      <c r="F23" s="51">
+      <c r="F23" s="49">
         <f t="shared" si="5"/>
         <v>0.94491766042021574</v>
       </c>
-      <c r="G23" s="59">
+      <c r="G23" s="57">
         <f>'Cost Plan'!$E$26/F23</f>
         <v>34542692.307692312</v>
       </c>

--- a/cost-plans/Urban-Highway-Improvement-Scheme.xlsx
+++ b/cost-plans/Urban-Highway-Improvement-Scheme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\qs\project-cost-control\cost-plans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D075570-FCE9-4D2B-9F85-FA1AAA67A567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F23B4E7-0FE0-488C-9E11-77D345605394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14092" activeTab="1" xr2:uid="{0C8C6BE1-598D-4333-9AA5-A074653745B1}"/>
   </bookViews>
@@ -523,13 +523,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -547,6 +543,10 @@
     <xf numFmtId="165" fontId="0" fillId="5" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="37" fontId="1" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="37" fontId="4" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="37" fontId="4" fillId="6" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="37" fontId="1" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2493,7 +2493,7 @@
         <f t="shared" si="0"/>
         <v>1580000</v>
       </c>
-      <c r="I5" s="34">
+      <c r="I5" s="54">
         <f>E5-H5</f>
         <v>-120000</v>
       </c>
@@ -2509,24 +2509,24 @@
       <c r="B6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="34">
         <v>640000</v>
       </c>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35">
+      <c r="D6" s="34"/>
+      <c r="E6" s="34">
         <f t="shared" ref="E6:E25" si="1">SUM(C6:D6)</f>
         <v>640000</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="34">
         <v>640000</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="34">
         <v>640000</v>
       </c>
-      <c r="H6" s="35">
+      <c r="H6" s="34">
         <v>640000</v>
       </c>
-      <c r="I6" s="36">
+      <c r="I6" s="55">
         <f t="shared" ref="I6:I25" si="2">E6-H6</f>
         <v>0</v>
       </c>
@@ -2541,24 +2541,24 @@
       <c r="B7" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="35">
         <v>320000</v>
       </c>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37">
+      <c r="D7" s="35"/>
+      <c r="E7" s="35">
         <f t="shared" si="1"/>
         <v>320000</v>
       </c>
-      <c r="F7" s="37">
+      <c r="F7" s="35">
         <v>320000</v>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="35">
         <v>320000</v>
       </c>
-      <c r="H7" s="37">
+      <c r="H7" s="35">
         <v>320000</v>
       </c>
-      <c r="I7" s="38">
+      <c r="I7" s="56">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2573,26 +2573,26 @@
       <c r="B8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="34">
         <v>320000</v>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="34">
         <v>180000</v>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="34">
         <f t="shared" ref="E8" si="3">SUM(C8:D8)</f>
         <v>500000</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="34">
         <v>480000</v>
       </c>
-      <c r="G8" s="35">
+      <c r="G8" s="34">
         <v>380000</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="34">
         <v>620000</v>
       </c>
-      <c r="I8" s="36">
+      <c r="I8" s="55">
         <f t="shared" ref="I8" si="4">E8-H8</f>
         <v>-120000</v>
       </c>
@@ -2631,7 +2631,7 @@
         <f>SUM(H10:H12)</f>
         <v>7100000</v>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="54">
         <f t="shared" si="2"/>
         <v>-605000</v>
       </c>
@@ -2647,26 +2647,26 @@
       <c r="B10" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="34">
         <v>3200000</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="34">
         <v>95000</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="34">
         <f t="shared" si="1"/>
         <v>3295000</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="34">
         <v>3295000</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="34">
         <v>2640000</v>
       </c>
-      <c r="H10" s="35">
+      <c r="H10" s="34">
         <v>3580000</v>
       </c>
-      <c r="I10" s="36">
+      <c r="I10" s="55">
         <f t="shared" si="2"/>
         <v>-285000</v>
       </c>
@@ -2681,24 +2681,24 @@
       <c r="B11" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="35">
         <v>2240000</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37">
+      <c r="D11" s="35"/>
+      <c r="E11" s="35">
         <f t="shared" si="1"/>
         <v>2240000</v>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="35">
         <v>1680000</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="35">
         <v>1344000</v>
       </c>
-      <c r="H11" s="37">
+      <c r="H11" s="35">
         <v>2420000</v>
       </c>
-      <c r="I11" s="38">
+      <c r="I11" s="56">
         <f t="shared" si="2"/>
         <v>-180000</v>
       </c>
@@ -2713,24 +2713,24 @@
       <c r="B12" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="34">
         <v>960000</v>
       </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35">
+      <c r="D12" s="34"/>
+      <c r="E12" s="34">
         <f t="shared" si="1"/>
         <v>960000</v>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="34">
         <v>720000</v>
       </c>
-      <c r="G12" s="35">
+      <c r="G12" s="34">
         <v>576000</v>
       </c>
-      <c r="H12" s="35">
+      <c r="H12" s="34">
         <v>1100000</v>
       </c>
-      <c r="I12" s="36">
+      <c r="I12" s="55">
         <f t="shared" si="2"/>
         <v>-140000</v>
       </c>
@@ -2769,7 +2769,7 @@
         <f t="shared" si="6"/>
         <v>5760000</v>
       </c>
-      <c r="I13" s="34">
+      <c r="I13" s="54">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2785,24 +2785,24 @@
       <c r="B14" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="34">
         <v>4480000</v>
       </c>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35">
+      <c r="D14" s="34"/>
+      <c r="E14" s="34">
         <f t="shared" si="1"/>
         <v>4480000</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="34">
         <v>2688000</v>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="34">
         <v>1344000</v>
       </c>
-      <c r="H14" s="35">
+      <c r="H14" s="34">
         <v>4480000</v>
       </c>
-      <c r="I14" s="36">
+      <c r="I14" s="55">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2817,24 +2817,24 @@
       <c r="B15" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="35">
         <v>1280000</v>
       </c>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37">
+      <c r="D15" s="35"/>
+      <c r="E15" s="35">
         <f t="shared" si="1"/>
         <v>1280000</v>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="35">
         <v>640000</v>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="35">
         <v>320000</v>
       </c>
-      <c r="H15" s="37">
+      <c r="H15" s="35">
         <v>1280000</v>
       </c>
-      <c r="I15" s="38">
+      <c r="I15" s="56">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2873,7 +2873,7 @@
         <f t="shared" si="7"/>
         <v>7650000</v>
       </c>
-      <c r="I16" s="34">
+      <c r="I16" s="54">
         <f t="shared" si="2"/>
         <v>-390000</v>
       </c>
@@ -2889,26 +2889,26 @@
       <c r="B17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="34">
         <v>4800000</v>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="34">
         <v>220000</v>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="34">
         <f t="shared" si="1"/>
         <v>5020000</v>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="34">
         <v>4320000</v>
       </c>
-      <c r="G17" s="35">
+      <c r="G17" s="34">
         <v>2880000</v>
       </c>
-      <c r="H17" s="35">
+      <c r="H17" s="34">
         <v>5200000</v>
       </c>
-      <c r="I17" s="36">
+      <c r="I17" s="55">
         <f t="shared" si="2"/>
         <v>-180000</v>
       </c>
@@ -2923,24 +2923,24 @@
       <c r="B18" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="37">
+      <c r="C18" s="35">
         <v>1600000</v>
       </c>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37">
+      <c r="D18" s="35"/>
+      <c r="E18" s="35">
         <f t="shared" si="1"/>
         <v>1600000</v>
       </c>
-      <c r="F18" s="37">
+      <c r="F18" s="35">
         <v>960000</v>
       </c>
-      <c r="G18" s="37">
+      <c r="G18" s="35">
         <v>576000</v>
       </c>
-      <c r="H18" s="37">
+      <c r="H18" s="35">
         <v>1750000</v>
       </c>
-      <c r="I18" s="38">
+      <c r="I18" s="56">
         <f t="shared" si="2"/>
         <v>-150000</v>
       </c>
@@ -2955,24 +2955,24 @@
       <c r="B19" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="34">
         <v>640000</v>
       </c>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35">
+      <c r="D19" s="34"/>
+      <c r="E19" s="34">
         <f t="shared" si="1"/>
         <v>640000</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="34">
         <v>384000</v>
       </c>
-      <c r="G19" s="35">
+      <c r="G19" s="34">
         <v>192000</v>
       </c>
-      <c r="H19" s="35">
+      <c r="H19" s="34">
         <v>700000</v>
       </c>
-      <c r="I19" s="36">
+      <c r="I19" s="55">
         <f t="shared" si="2"/>
         <v>-60000</v>
       </c>
@@ -3011,7 +3011,7 @@
         <f t="shared" si="8"/>
         <v>2560000</v>
       </c>
-      <c r="I20" s="34">
+      <c r="I20" s="54">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3027,24 +3027,24 @@
       <c r="B21" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="34">
         <v>1600000</v>
       </c>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35">
+      <c r="D21" s="34"/>
+      <c r="E21" s="34">
         <f t="shared" si="1"/>
         <v>1600000</v>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="34">
         <v>640000</v>
       </c>
-      <c r="G21" s="35">
+      <c r="G21" s="34">
         <v>320000</v>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="34">
         <v>1600000</v>
       </c>
-      <c r="I21" s="36">
+      <c r="I21" s="55">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3059,24 +3059,24 @@
       <c r="B22" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="37">
+      <c r="C22" s="35">
         <v>960000</v>
       </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37">
+      <c r="D22" s="35"/>
+      <c r="E22" s="35">
         <f t="shared" si="1"/>
         <v>960000</v>
       </c>
-      <c r="F22" s="37">
+      <c r="F22" s="35">
         <v>288000</v>
       </c>
-      <c r="G22" s="37">
+      <c r="G22" s="35">
         <v>144000</v>
       </c>
-      <c r="H22" s="37">
+      <c r="H22" s="35">
         <v>960000</v>
       </c>
-      <c r="I22" s="38">
+      <c r="I22" s="56">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3108,7 +3108,7 @@
       <c r="H23" s="33">
         <v>960000</v>
       </c>
-      <c r="I23" s="34">
+      <c r="I23" s="54">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3142,7 +3142,7 @@
       <c r="H24" s="33">
         <v>6200000</v>
       </c>
-      <c r="I24" s="34">
+      <c r="I24" s="54">
         <f t="shared" si="2"/>
         <v>-295000</v>
       </c>
@@ -3174,7 +3174,7 @@
       <c r="H25" s="33">
         <v>1800000</v>
       </c>
-      <c r="I25" s="34">
+      <c r="I25" s="54">
         <f t="shared" si="2"/>
         <v>440000</v>
       </c>
@@ -3186,31 +3186,31 @@
       <c r="B26" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="39">
+      <c r="C26" s="36">
         <f>SUM(C5,C9,C13,C16,C20,C23,C24,C25)</f>
         <v>32000000</v>
       </c>
-      <c r="D26" s="39">
+      <c r="D26" s="36">
         <f t="shared" ref="D26:H26" si="9">SUM(D5,D9,D13,D16,D20,D23,D24,D25)</f>
         <v>640000</v>
       </c>
-      <c r="E26" s="39">
+      <c r="E26" s="36">
         <f t="shared" si="9"/>
         <v>32640000</v>
       </c>
-      <c r="F26" s="39">
+      <c r="F26" s="36">
         <f t="shared" si="9"/>
         <v>23152000</v>
       </c>
-      <c r="G26" s="39">
+      <c r="G26" s="36">
         <f t="shared" si="9"/>
         <v>14638500</v>
       </c>
-      <c r="H26" s="39">
+      <c r="H26" s="36">
         <f t="shared" si="9"/>
         <v>33610000</v>
       </c>
-      <c r="I26" s="40">
+      <c r="I26" s="57">
         <f>E26-H26</f>
         <v>-970000</v>
       </c>
@@ -3278,51 +3278,51 @@
       <c r="G2" s="59"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="F4" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="39" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A5" s="50">
+      <c r="A5" s="46">
         <v>45170</v>
       </c>
-      <c r="B5" s="51">
+      <c r="B5" s="47">
         <v>480000</v>
       </c>
-      <c r="C5" s="51">
+      <c r="C5" s="47">
         <v>510000</v>
       </c>
-      <c r="D5" s="52">
+      <c r="D5" s="48">
         <f>B5-C5</f>
         <v>-30000</v>
       </c>
-      <c r="E5" s="53">
+      <c r="E5" s="49">
         <f>D5/B5</f>
         <v>-6.25E-2</v>
       </c>
-      <c r="F5" s="54">
+      <c r="F5" s="50">
         <f>B5/C5</f>
         <v>0.94117647058823528</v>
       </c>
-      <c r="G5" s="55">
+      <c r="G5" s="51">
         <f>'Cost Plan'!$E$26/F5</f>
         <v>34680000</v>
       </c>
@@ -3345,7 +3345,7 @@
         <f t="shared" ref="E6:E10" si="1">D6/B6</f>
         <v>-7.1428571428571425E-2</v>
       </c>
-      <c r="F6" s="45">
+      <c r="F6" s="41">
         <f t="shared" ref="F6:F10" si="2">B6/C6</f>
         <v>0.93333333333333335</v>
       </c>
@@ -3372,7 +3372,7 @@
         <f t="shared" si="1"/>
         <v>-7.8787878787878782E-2</v>
       </c>
-      <c r="F7" s="44">
+      <c r="F7" s="40">
         <f t="shared" si="2"/>
         <v>0.9269662921348315</v>
       </c>
@@ -3399,7 +3399,7 @@
         <f t="shared" si="1"/>
         <v>-8.5714285714285715E-2</v>
       </c>
-      <c r="F8" s="45">
+      <c r="F8" s="41">
         <f t="shared" si="2"/>
         <v>0.92105263157894735</v>
       </c>
@@ -3426,7 +3426,7 @@
         <f t="shared" si="1"/>
         <v>-8.1560283687943269E-2</v>
       </c>
-      <c r="F9" s="44">
+      <c r="F9" s="40">
         <f t="shared" si="2"/>
         <v>0.92459016393442628</v>
       </c>
@@ -3453,7 +3453,7 @@
         <f t="shared" si="1"/>
         <v>-8.1521739130434784E-2</v>
       </c>
-      <c r="F10" s="45">
+      <c r="F10" s="41">
         <f t="shared" si="2"/>
         <v>0.92462311557788945</v>
       </c>
@@ -3480,7 +3480,7 @@
         <f t="shared" ref="E11:E23" si="4">D11/B11</f>
         <v>-6.6666666666666666E-2</v>
       </c>
-      <c r="F11" s="44">
+      <c r="F11" s="40">
         <f t="shared" ref="F11:F23" si="5">B11/C11</f>
         <v>0.9375</v>
       </c>
@@ -3507,7 +3507,7 @@
         <f t="shared" si="4"/>
         <v>-6.0897435897435896E-2</v>
       </c>
-      <c r="F12" s="45">
+      <c r="F12" s="41">
         <f t="shared" si="5"/>
         <v>0.94259818731117828</v>
       </c>
@@ -3534,7 +3534,7 @@
         <f t="shared" si="4"/>
         <v>-5.46875E-2</v>
       </c>
-      <c r="F13" s="44">
+      <c r="F13" s="40">
         <f t="shared" si="5"/>
         <v>0.94814814814814818</v>
       </c>
@@ -3561,7 +3561,7 @@
         <f t="shared" si="4"/>
         <v>-5.8114035087719298E-2</v>
       </c>
-      <c r="F14" s="45">
+      <c r="F14" s="41">
         <f t="shared" si="5"/>
         <v>0.94507772020725389</v>
       </c>
@@ -3588,7 +3588,7 @@
         <f t="shared" si="4"/>
         <v>-5.587121212121212E-2</v>
       </c>
-      <c r="F15" s="44">
+      <c r="F15" s="40">
         <f t="shared" si="5"/>
         <v>0.94708520179372202</v>
       </c>
@@ -3615,7 +3615,7 @@
         <f t="shared" si="4"/>
         <v>-5.5084745762711863E-2</v>
       </c>
-      <c r="F16" s="45">
+      <c r="F16" s="41">
         <f t="shared" si="5"/>
         <v>0.94779116465863456</v>
       </c>
@@ -3642,7 +3642,7 @@
         <f t="shared" si="4"/>
         <v>-5.4054054054054057E-2</v>
       </c>
-      <c r="F17" s="44">
+      <c r="F17" s="40">
         <f t="shared" si="5"/>
         <v>0.94871794871794868</v>
       </c>
@@ -3669,7 +3669,7 @@
         <f t="shared" si="4"/>
         <v>-5.2442528735632182E-2</v>
       </c>
-      <c r="F18" s="45">
+      <c r="F18" s="41">
         <f t="shared" si="5"/>
         <v>0.95017064846416377</v>
       </c>
@@ -3696,7 +3696,7 @@
         <f t="shared" si="4"/>
         <v>-5.2559726962457337E-2</v>
       </c>
-      <c r="F19" s="44">
+      <c r="F19" s="40">
         <f t="shared" si="5"/>
         <v>0.95006485084306092</v>
       </c>
@@ -3723,7 +3723,7 @@
         <f t="shared" si="4"/>
         <v>-5.2356020942408377E-2</v>
       </c>
-      <c r="F20" s="45">
+      <c r="F20" s="41">
         <f t="shared" si="5"/>
         <v>0.95024875621890548</v>
       </c>
@@ -3750,7 +3750,7 @@
         <f t="shared" si="4"/>
         <v>-5.2465233881163087E-2</v>
       </c>
-      <c r="F21" s="44">
+      <c r="F21" s="40">
         <f t="shared" si="5"/>
         <v>0.95015015015015014</v>
       </c>
@@ -3777,7 +3777,7 @@
         <f t="shared" si="4"/>
         <v>-5.2307692307692305E-2</v>
       </c>
-      <c r="F22" s="45">
+      <c r="F22" s="41">
         <f t="shared" si="5"/>
         <v>0.95029239766081874</v>
       </c>
@@ -3787,28 +3787,28 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A23" s="56">
+      <c r="A23" s="52">
         <v>45717</v>
       </c>
-      <c r="B23" s="46">
+      <c r="B23" s="42">
         <v>16640000</v>
       </c>
-      <c r="C23" s="46">
+      <c r="C23" s="42">
         <v>17610000</v>
       </c>
-      <c r="D23" s="47">
+      <c r="D23" s="43">
         <f t="shared" si="3"/>
         <v>-970000</v>
       </c>
-      <c r="E23" s="48">
+      <c r="E23" s="44">
         <f t="shared" si="4"/>
         <v>-5.8293269230769232E-2</v>
       </c>
-      <c r="F23" s="49">
+      <c r="F23" s="45">
         <f t="shared" si="5"/>
         <v>0.94491766042021574</v>
       </c>
-      <c r="G23" s="57">
+      <c r="G23" s="53">
         <f>'Cost Plan'!$E$26/F23</f>
         <v>34542692.307692312</v>
       </c>

--- a/cost-plans/Urban-Highway-Improvement-Scheme.xlsx
+++ b/cost-plans/Urban-Highway-Improvement-Scheme.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F23B4E7-0FE0-488C-9E11-77D345605394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14092" activeTab="1" xr2:uid="{0C8C6BE1-598D-4333-9AA5-A074653745B1}"/>
+    <workbookView xWindow="4714" yWindow="1706" windowWidth="18515" windowHeight="10123" xr2:uid="{0C8C6BE1-598D-4333-9AA5-A074653745B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Cost Plan" sheetId="1" r:id="rId1"/>

--- a/cost-plans/Urban-Highway-Improvement-Scheme.xlsx
+++ b/cost-plans/Urban-Highway-Improvement-Scheme.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\qs\project-cost-control\cost-plans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F23B4E7-0FE0-488C-9E11-77D345605394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E009FF16-9A9C-4360-BE28-CC4512D0DC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4714" yWindow="1706" windowWidth="18515" windowHeight="10123" xr2:uid="{0C8C6BE1-598D-4333-9AA5-A074653745B1}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14092" xr2:uid="{0C8C6BE1-598D-4333-9AA5-A074653745B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Cost Plan" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="78">
   <si>
     <t>Project Name</t>
   </si>
@@ -269,17 +269,22 @@
   </si>
   <si>
     <t>Landscaping &amp; Ecology</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>Infrastructure</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="&quot;£&quot;#,##0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -510,9 +515,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="14" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -552,6 +554,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2402,33 +2407,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="35.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="59" t="str">
+      <c r="A2" s="58" t="str">
         <f ca="1">"Meridian Cost Consultants | Report Date: "&amp;TEXT(TODAY(),"DD MMMM YYYY")</f>
-        <v>Meridian Cost Consultants | Report Date: 15 May 2026</v>
-      </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
+        <v>Meridian Cost Consultants | Report Date: 16 May 2026</v>
+      </c>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
@@ -2469,31 +2474,31 @@
       <c r="B5" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="32">
         <f>SUM(C6:C8)</f>
         <v>1280000</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="32">
         <f t="shared" ref="D5:H5" si="0">SUM(D6:D8)</f>
         <v>180000</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="32">
         <f t="shared" si="0"/>
         <v>1460000</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="32">
         <f t="shared" si="0"/>
         <v>1440000</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="32">
         <f t="shared" si="0"/>
         <v>1340000</v>
       </c>
-      <c r="H5" s="33">
+      <c r="H5" s="32">
         <f t="shared" si="0"/>
         <v>1580000</v>
       </c>
-      <c r="I5" s="54">
+      <c r="I5" s="53">
         <f>E5-H5</f>
         <v>-120000</v>
       </c>
@@ -2509,24 +2514,24 @@
       <c r="B6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="33">
         <v>640000</v>
       </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34">
+      <c r="D6" s="33"/>
+      <c r="E6" s="33">
         <f t="shared" ref="E6:E25" si="1">SUM(C6:D6)</f>
         <v>640000</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="33">
         <v>640000</v>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="33">
         <v>640000</v>
       </c>
-      <c r="H6" s="34">
+      <c r="H6" s="33">
         <v>640000</v>
       </c>
-      <c r="I6" s="55">
+      <c r="I6" s="54">
         <f t="shared" ref="I6:I25" si="2">E6-H6</f>
         <v>0</v>
       </c>
@@ -2541,24 +2546,24 @@
       <c r="B7" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="34">
         <v>320000</v>
       </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35">
+      <c r="D7" s="34"/>
+      <c r="E7" s="34">
         <f t="shared" si="1"/>
         <v>320000</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="34">
         <v>320000</v>
       </c>
-      <c r="G7" s="35">
+      <c r="G7" s="34">
         <v>320000</v>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="34">
         <v>320000</v>
       </c>
-      <c r="I7" s="56">
+      <c r="I7" s="55">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2573,26 +2578,26 @@
       <c r="B8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="33">
         <v>320000</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="33">
         <v>180000</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="33">
         <f t="shared" ref="E8" si="3">SUM(C8:D8)</f>
         <v>500000</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="33">
         <v>480000</v>
       </c>
-      <c r="G8" s="34">
+      <c r="G8" s="33">
         <v>380000</v>
       </c>
-      <c r="H8" s="34">
+      <c r="H8" s="33">
         <v>620000</v>
       </c>
-      <c r="I8" s="55">
+      <c r="I8" s="54">
         <f t="shared" ref="I8" si="4">E8-H8</f>
         <v>-120000</v>
       </c>
@@ -2607,31 +2612,31 @@
       <c r="B9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="32">
         <f>SUM(C10:C12)</f>
         <v>6400000</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="32">
         <f t="shared" ref="D9:G9" si="5">SUM(D10:D12)</f>
         <v>95000</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="32">
         <f t="shared" si="5"/>
         <v>6495000</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="32">
         <f t="shared" si="5"/>
         <v>5695000</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="32">
         <f t="shared" si="5"/>
         <v>4560000</v>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="32">
         <f>SUM(H10:H12)</f>
         <v>7100000</v>
       </c>
-      <c r="I9" s="54">
+      <c r="I9" s="53">
         <f t="shared" si="2"/>
         <v>-605000</v>
       </c>
@@ -2647,26 +2652,26 @@
       <c r="B10" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="33">
         <v>3200000</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <v>95000</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <f t="shared" si="1"/>
         <v>3295000</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="33">
         <v>3295000</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="33">
         <v>2640000</v>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="33">
         <v>3580000</v>
       </c>
-      <c r="I10" s="55">
+      <c r="I10" s="54">
         <f t="shared" si="2"/>
         <v>-285000</v>
       </c>
@@ -2681,24 +2686,24 @@
       <c r="B11" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="34">
         <v>2240000</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35">
+      <c r="D11" s="34"/>
+      <c r="E11" s="34">
         <f t="shared" si="1"/>
         <v>2240000</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="34">
         <v>1680000</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="34">
         <v>1344000</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="34">
         <v>2420000</v>
       </c>
-      <c r="I11" s="56">
+      <c r="I11" s="55">
         <f t="shared" si="2"/>
         <v>-180000</v>
       </c>
@@ -2713,24 +2718,24 @@
       <c r="B12" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="33">
         <v>960000</v>
       </c>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34">
+      <c r="D12" s="33"/>
+      <c r="E12" s="33">
         <f t="shared" si="1"/>
         <v>960000</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="33">
         <v>720000</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="33">
         <v>576000</v>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="33">
         <v>1100000</v>
       </c>
-      <c r="I12" s="55">
+      <c r="I12" s="54">
         <f t="shared" si="2"/>
         <v>-140000</v>
       </c>
@@ -2745,31 +2750,31 @@
       <c r="B13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="32">
         <f>SUM(C14:C15)</f>
         <v>5760000</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="32">
         <f t="shared" ref="D13:H13" si="6">SUM(D14:D15)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="32">
         <f t="shared" si="6"/>
         <v>5760000</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="32">
         <f t="shared" si="6"/>
         <v>3328000</v>
       </c>
-      <c r="G13" s="33">
+      <c r="G13" s="32">
         <f t="shared" si="6"/>
         <v>1664000</v>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="32">
         <f t="shared" si="6"/>
         <v>5760000</v>
       </c>
-      <c r="I13" s="54">
+      <c r="I13" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2785,24 +2790,24 @@
       <c r="B14" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="33">
         <v>4480000</v>
       </c>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34">
+      <c r="D14" s="33"/>
+      <c r="E14" s="33">
         <f t="shared" si="1"/>
         <v>4480000</v>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="33">
         <v>2688000</v>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="33">
         <v>1344000</v>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="33">
         <v>4480000</v>
       </c>
-      <c r="I14" s="55">
+      <c r="I14" s="54">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2817,24 +2822,24 @@
       <c r="B15" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="34">
         <v>1280000</v>
       </c>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35">
+      <c r="D15" s="34"/>
+      <c r="E15" s="34">
         <f t="shared" si="1"/>
         <v>1280000</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="34">
         <v>640000</v>
       </c>
-      <c r="G15" s="35">
+      <c r="G15" s="34">
         <v>320000</v>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="34">
         <v>1280000</v>
       </c>
-      <c r="I15" s="56">
+      <c r="I15" s="55">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2849,31 +2854,31 @@
       <c r="B16" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="32">
         <f>SUM(C17:C19)</f>
         <v>7040000</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="32">
         <f t="shared" ref="D16:H16" si="7">SUM(D17:D19)</f>
         <v>220000</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="32">
         <f t="shared" si="7"/>
         <v>7260000</v>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="32">
         <f t="shared" si="7"/>
         <v>5664000</v>
       </c>
-      <c r="G16" s="33">
+      <c r="G16" s="32">
         <f t="shared" si="7"/>
         <v>3648000</v>
       </c>
-      <c r="H16" s="33">
+      <c r="H16" s="32">
         <f t="shared" si="7"/>
         <v>7650000</v>
       </c>
-      <c r="I16" s="54">
+      <c r="I16" s="53">
         <f t="shared" si="2"/>
         <v>-390000</v>
       </c>
@@ -2889,26 +2894,26 @@
       <c r="B17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="33">
         <v>4800000</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="33">
         <v>220000</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="33">
         <f t="shared" si="1"/>
         <v>5020000</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="33">
         <v>4320000</v>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="33">
         <v>2880000</v>
       </c>
-      <c r="H17" s="34">
+      <c r="H17" s="33">
         <v>5200000</v>
       </c>
-      <c r="I17" s="55">
+      <c r="I17" s="54">
         <f t="shared" si="2"/>
         <v>-180000</v>
       </c>
@@ -2923,24 +2928,24 @@
       <c r="B18" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="34">
         <v>1600000</v>
       </c>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35">
+      <c r="D18" s="34"/>
+      <c r="E18" s="34">
         <f t="shared" si="1"/>
         <v>1600000</v>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="34">
         <v>960000</v>
       </c>
-      <c r="G18" s="35">
+      <c r="G18" s="34">
         <v>576000</v>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="34">
         <v>1750000</v>
       </c>
-      <c r="I18" s="56">
+      <c r="I18" s="55">
         <f t="shared" si="2"/>
         <v>-150000</v>
       </c>
@@ -2955,24 +2960,24 @@
       <c r="B19" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="33">
         <v>640000</v>
       </c>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34">
+      <c r="D19" s="33"/>
+      <c r="E19" s="33">
         <f t="shared" si="1"/>
         <v>640000</v>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="33">
         <v>384000</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="33">
         <v>192000</v>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="33">
         <v>700000</v>
       </c>
-      <c r="I19" s="55">
+      <c r="I19" s="54">
         <f t="shared" si="2"/>
         <v>-60000</v>
       </c>
@@ -2987,31 +2992,31 @@
       <c r="B20" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="32">
         <f>SUM(C21:C22)</f>
         <v>2560000</v>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="32">
         <f t="shared" ref="D20:H20" si="8">SUM(D21:D22)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="32">
         <f t="shared" si="8"/>
         <v>2560000</v>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="32">
         <f t="shared" si="8"/>
         <v>928000</v>
       </c>
-      <c r="G20" s="33">
+      <c r="G20" s="32">
         <f t="shared" si="8"/>
         <v>464000</v>
       </c>
-      <c r="H20" s="33">
+      <c r="H20" s="32">
         <f t="shared" si="8"/>
         <v>2560000</v>
       </c>
-      <c r="I20" s="54">
+      <c r="I20" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3027,24 +3032,24 @@
       <c r="B21" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="33">
         <v>1600000</v>
       </c>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34">
+      <c r="D21" s="33"/>
+      <c r="E21" s="33">
         <f t="shared" si="1"/>
         <v>1600000</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="33">
         <v>640000</v>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="33">
         <v>320000</v>
       </c>
-      <c r="H21" s="34">
+      <c r="H21" s="33">
         <v>1600000</v>
       </c>
-      <c r="I21" s="55">
+      <c r="I21" s="54">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3059,24 +3064,24 @@
       <c r="B22" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="34">
         <v>960000</v>
       </c>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35">
+      <c r="D22" s="34"/>
+      <c r="E22" s="34">
         <f t="shared" si="1"/>
         <v>960000</v>
       </c>
-      <c r="F22" s="35">
+      <c r="F22" s="34">
         <v>288000</v>
       </c>
-      <c r="G22" s="35">
+      <c r="G22" s="34">
         <v>144000</v>
       </c>
-      <c r="H22" s="35">
+      <c r="H22" s="34">
         <v>960000</v>
       </c>
-      <c r="I22" s="56">
+      <c r="I22" s="55">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3091,24 +3096,24 @@
       <c r="B23" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="33">
+      <c r="C23" s="32">
         <v>960000</v>
       </c>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33">
+      <c r="D23" s="32"/>
+      <c r="E23" s="32">
         <f t="shared" si="1"/>
         <v>960000</v>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="32">
         <v>192000</v>
       </c>
-      <c r="G23" s="33">
+      <c r="G23" s="32">
         <v>0</v>
       </c>
-      <c r="H23" s="33">
+      <c r="H23" s="32">
         <v>960000</v>
       </c>
-      <c r="I23" s="54">
+      <c r="I23" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3123,26 +3128,26 @@
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C24" s="32">
         <v>5760000</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="32">
         <v>145000</v>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="32">
         <f t="shared" si="1"/>
         <v>5905000</v>
       </c>
-      <c r="F24" s="33">
+      <c r="F24" s="32">
         <v>5905000</v>
       </c>
-      <c r="G24" s="33">
+      <c r="G24" s="32">
         <v>2962500</v>
       </c>
-      <c r="H24" s="33">
+      <c r="H24" s="32">
         <v>6200000</v>
       </c>
-      <c r="I24" s="54">
+      <c r="I24" s="53">
         <f t="shared" si="2"/>
         <v>-295000</v>
       </c>
@@ -3157,24 +3162,24 @@
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="32">
         <v>2240000</v>
       </c>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33">
+      <c r="D25" s="32"/>
+      <c r="E25" s="32">
         <f t="shared" si="1"/>
         <v>2240000</v>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="32">
         <v>0</v>
       </c>
-      <c r="G25" s="33">
+      <c r="G25" s="32">
         <v>0</v>
       </c>
-      <c r="H25" s="33">
+      <c r="H25" s="32">
         <v>1800000</v>
       </c>
-      <c r="I25" s="54">
+      <c r="I25" s="53">
         <f t="shared" si="2"/>
         <v>440000</v>
       </c>
@@ -3186,31 +3191,31 @@
       <c r="B26" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="36">
+      <c r="C26" s="35">
         <f>SUM(C5,C9,C13,C16,C20,C23,C24,C25)</f>
         <v>32000000</v>
       </c>
-      <c r="D26" s="36">
+      <c r="D26" s="35">
         <f t="shared" ref="D26:H26" si="9">SUM(D5,D9,D13,D16,D20,D23,D24,D25)</f>
         <v>640000</v>
       </c>
-      <c r="E26" s="36">
+      <c r="E26" s="35">
         <f t="shared" si="9"/>
         <v>32640000</v>
       </c>
-      <c r="F26" s="36">
+      <c r="F26" s="35">
         <f t="shared" si="9"/>
         <v>23152000</v>
       </c>
-      <c r="G26" s="36">
+      <c r="G26" s="35">
         <f t="shared" si="9"/>
         <v>14638500</v>
       </c>
-      <c r="H26" s="36">
+      <c r="H26" s="35">
         <f t="shared" si="9"/>
         <v>33610000</v>
       </c>
-      <c r="I26" s="57">
+      <c r="I26" s="56">
         <f>E26-H26</f>
         <v>-970000</v>
       </c>
@@ -3256,73 +3261,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="35.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="39" t="s">
+      <c r="G4" s="38" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A5" s="46">
+      <c r="A5" s="45">
         <v>45170</v>
       </c>
-      <c r="B5" s="47">
+      <c r="B5" s="46">
         <v>480000</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="46">
         <v>510000</v>
       </c>
-      <c r="D5" s="48">
+      <c r="D5" s="47">
         <f>B5-C5</f>
         <v>-30000</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="48">
         <f>D5/B5</f>
         <v>-6.25E-2</v>
       </c>
-      <c r="F5" s="50">
+      <c r="F5" s="49">
         <f>B5/C5</f>
         <v>0.94117647058823528</v>
       </c>
-      <c r="G5" s="51">
+      <c r="G5" s="50">
         <f>'Cost Plan'!$E$26/F5</f>
         <v>34680000</v>
       </c>
@@ -3345,7 +3350,7 @@
         <f t="shared" ref="E6:E10" si="1">D6/B6</f>
         <v>-7.1428571428571425E-2</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="40">
         <f t="shared" ref="F6:F10" si="2">B6/C6</f>
         <v>0.93333333333333335</v>
       </c>
@@ -3372,7 +3377,7 @@
         <f t="shared" si="1"/>
         <v>-7.8787878787878782E-2</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="39">
         <f t="shared" si="2"/>
         <v>0.9269662921348315</v>
       </c>
@@ -3399,7 +3404,7 @@
         <f t="shared" si="1"/>
         <v>-8.5714285714285715E-2</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="40">
         <f t="shared" si="2"/>
         <v>0.92105263157894735</v>
       </c>
@@ -3426,7 +3431,7 @@
         <f t="shared" si="1"/>
         <v>-8.1560283687943269E-2</v>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="39">
         <f t="shared" si="2"/>
         <v>0.92459016393442628</v>
       </c>
@@ -3453,7 +3458,7 @@
         <f t="shared" si="1"/>
         <v>-8.1521739130434784E-2</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="40">
         <f t="shared" si="2"/>
         <v>0.92462311557788945</v>
       </c>
@@ -3480,7 +3485,7 @@
         <f t="shared" ref="E11:E23" si="4">D11/B11</f>
         <v>-6.6666666666666666E-2</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="39">
         <f t="shared" ref="F11:F23" si="5">B11/C11</f>
         <v>0.9375</v>
       </c>
@@ -3507,7 +3512,7 @@
         <f t="shared" si="4"/>
         <v>-6.0897435897435896E-2</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="40">
         <f t="shared" si="5"/>
         <v>0.94259818731117828</v>
       </c>
@@ -3534,7 +3539,7 @@
         <f t="shared" si="4"/>
         <v>-5.46875E-2</v>
       </c>
-      <c r="F13" s="40">
+      <c r="F13" s="39">
         <f t="shared" si="5"/>
         <v>0.94814814814814818</v>
       </c>
@@ -3561,7 +3566,7 @@
         <f t="shared" si="4"/>
         <v>-5.8114035087719298E-2</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="40">
         <f t="shared" si="5"/>
         <v>0.94507772020725389</v>
       </c>
@@ -3588,7 +3593,7 @@
         <f t="shared" si="4"/>
         <v>-5.587121212121212E-2</v>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="39">
         <f t="shared" si="5"/>
         <v>0.94708520179372202</v>
       </c>
@@ -3615,7 +3620,7 @@
         <f t="shared" si="4"/>
         <v>-5.5084745762711863E-2</v>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="40">
         <f t="shared" si="5"/>
         <v>0.94779116465863456</v>
       </c>
@@ -3642,7 +3647,7 @@
         <f t="shared" si="4"/>
         <v>-5.4054054054054057E-2</v>
       </c>
-      <c r="F17" s="40">
+      <c r="F17" s="39">
         <f t="shared" si="5"/>
         <v>0.94871794871794868</v>
       </c>
@@ -3669,7 +3674,7 @@
         <f t="shared" si="4"/>
         <v>-5.2442528735632182E-2</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="40">
         <f t="shared" si="5"/>
         <v>0.95017064846416377</v>
       </c>
@@ -3696,7 +3701,7 @@
         <f t="shared" si="4"/>
         <v>-5.2559726962457337E-2</v>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="39">
         <f t="shared" si="5"/>
         <v>0.95006485084306092</v>
       </c>
@@ -3723,7 +3728,7 @@
         <f t="shared" si="4"/>
         <v>-5.2356020942408377E-2</v>
       </c>
-      <c r="F20" s="41">
+      <c r="F20" s="40">
         <f t="shared" si="5"/>
         <v>0.95024875621890548</v>
       </c>
@@ -3750,7 +3755,7 @@
         <f t="shared" si="4"/>
         <v>-5.2465233881163087E-2</v>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="39">
         <f t="shared" si="5"/>
         <v>0.95015015015015014</v>
       </c>
@@ -3777,7 +3782,7 @@
         <f t="shared" si="4"/>
         <v>-5.2307692307692305E-2</v>
       </c>
-      <c r="F22" s="41">
+      <c r="F22" s="40">
         <f t="shared" si="5"/>
         <v>0.95029239766081874</v>
       </c>
@@ -3787,28 +3792,28 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A23" s="52">
+      <c r="A23" s="51">
         <v>45717</v>
       </c>
-      <c r="B23" s="42">
+      <c r="B23" s="41">
         <v>16640000</v>
       </c>
-      <c r="C23" s="42">
+      <c r="C23" s="41">
         <v>17610000</v>
       </c>
-      <c r="D23" s="43">
+      <c r="D23" s="42">
         <f t="shared" si="3"/>
         <v>-970000</v>
       </c>
-      <c r="E23" s="44">
+      <c r="E23" s="43">
         <f t="shared" si="4"/>
         <v>-5.8293269230769232E-2</v>
       </c>
-      <c r="F23" s="45">
+      <c r="F23" s="44">
         <f t="shared" si="5"/>
         <v>0.94491766042021574</v>
       </c>
-      <c r="G23" s="53">
+      <c r="G23" s="52">
         <f>'Cost Plan'!$E$26/F23</f>
         <v>34542692.307692312</v>
       </c>
@@ -3843,7 +3848,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2FB73FC-2423-441D-B32D-DF5AF30B74F5}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="25.69140625" bestFit="1" customWidth="1"/>
@@ -3878,7 +3883,7 @@
       <c r="A4" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="59">
         <v>32000000</v>
       </c>
     </row>
@@ -3886,7 +3891,7 @@
       <c r="A5" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="29">
         <v>45170</v>
       </c>
     </row>
@@ -3894,7 +3899,7 @@
       <c r="A6" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="30">
         <v>46081</v>
       </c>
     </row>
@@ -3918,9 +3923,17 @@
       <c r="A9" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="31">
         <f>'Cost Plan'!J26</f>
         <v>0.45094348019581665</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
